--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/region-del-biobio.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/region-del-biobio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,37 +514,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>654-278-CM26</t>
+          <t>2410-10-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.820.004-3</t>
+          <t>69.170.102-6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>OFISILLAS CHILE SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.855.435-8</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,33 +569,33 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>17071.99</v>
+        <v>5624.23</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1389183-367-CM26</t>
+          <t>1305504-30-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>INTERGROUPE S.A.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>76.719.470-6</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,43 +630,43 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>59729.87</v>
+        <v>24518.65</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2704-1693-CM26</t>
+          <t>1208910-41-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>60.911.006-6</t>
+          <t>65.201.852-1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DEL BIO BIO</t>
+          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL DE LA REGIÓN DEL BIOBÍO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>COMERCIAL VYB SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.583.479-1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,43 +691,43 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>6464.65</v>
+        <v>34905.96</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4083-414-CM26</t>
+          <t>1057417-15445-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.151.002-6</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABRERO</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>COMERCIAL RENHET SPA</t>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>77.619.564-2</t>
+          <t>76.058.118-6</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,28 +752,28 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>13074.04</v>
+        <v>6610.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1057934-17-CM26</t>
+          <t>1057931-1-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.607.202-1</t>
+          <t>61.607.200-5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE TALCAHUANO HOSPITAL</t>
+          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,6 +813,1409 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
+        <v>6896.54</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1057931-2-CM25</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>61.607.200-5</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Biobío </t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>77.346.435-9</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>6896.54</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>652-127-CM25</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>61.954.500-1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARAUCO</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Biobío </t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA MERCADO PUBLICO SPA</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>76.559.762-5</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>5564.64</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2178-117-CM25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>60.301.001-9</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Biobío </t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>76.058.118-6</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>16405.53</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>4375-1529-CM25</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>61.602.189-3</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HOSPITAL GUILLERMO GRANT BENAVENTE DE CO</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Biobío </t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>suria ltda</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>77.827.520-1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>6179.38</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1426098-160-CM25</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Biobío </t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>LEFI SPA</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>23292.34</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2421-3979-CM25</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>69.256.900-8</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Biobío </t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>FRANCISCO ANTONIO PALACIOS MUÑOZ</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>14.164.209-K</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>7126.39</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>4229-79-CM25</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>61.954.400-5</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Biobío </t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>LEFI SPA</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>15430.84</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2421-4025-CM25</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>69.256.900-8</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Biobío </t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>CLINICON SPA</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>77.070.635-1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>10291.28</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2888-39-CM25</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>60.911.006-6</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Biobío </t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>7195.48</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1550-20-CM25</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>60.803.000-k</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Biobío </t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>25027.85</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2410-383-CM25</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>69.170.102-6</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Biobío </t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>92.999.000-5</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>22197.36</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>4083-435-CM25</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>69.151.002-6</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Biobío </t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Inversiones Cuatro Rios S.A.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>76.094.593-5</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>11999.41</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1057931-52-CM25</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>61.607.200-5</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Biobío </t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>10404.71</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>3076-329-CM25</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>61.102.022-8</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Biobío </t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>13824.03</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1057931-84-CM25</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>61.607.200-5</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Biobío </t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>LEFI SPA</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>11047.77</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2410-558-CM25</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>69.170.102-6</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Biobío </t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>7501.23</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1057931-110-CM25</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>61.607.200-5</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Biobío </t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>LEFI SPA</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>9022.9</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1079576-4068-CM25</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>61.954.400-5</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Biobío </t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>LEFI SPA</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>18734.57</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>654-278-CM26</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>61.820.004-3</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Biobío </t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>17071.99</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1389183-367-CM26</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>61.981.100-3</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN COSTA</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Biobío </t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>JUEGOS MAGICOS</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>59729.87</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2704-1693-CM26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>60.911.006-6</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Biobío </t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>6464.65</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>4083-414-CM26</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>69.151.002-6</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Biobío </t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>COMERCIAL RENHET SPA</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>77.619.564-2</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>13074.04</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1057934-17-CM26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>61.607.202-1</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DE TALCAHUANO HOSPITAL</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Biobío </t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="n">
         <v>10291.91</v>
       </c>
     </row>
